--- a/analysis/SecurityMatrix.xlsx
+++ b/analysis/SecurityMatrix.xlsx
@@ -1064,7 +1064,7 @@
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d161086-4829-409f-9f75-5bde88dcb151">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="42d8e6db-7b1e-4a51-8fbb-e5e83cc76820"/>
+    <TaxCatchAll xmlns="42d8e6db-7b1e-4a51-8fbb-e5e83cc76820" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>

--- a/analysis/SecurityMatrix.xlsx
+++ b/analysis/SecurityMatrix.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://evri.sharepoint.com/sites/ukho-meds/Shared Documents/MEDS DB/analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{C56095F7-88C3-4CD6-8E98-1CCCE51BBC9B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{71EEB02E-2714-4A85-A0DF-8C84F083C3C5}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{C56095F7-88C3-4CD6-8E98-1CCCE51BBC9B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{1BAF2C19-1CCB-4505-8F9C-2234CC5EE840}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="16605" xr2:uid="{148B9DD2-970A-4207-80A7-5D825751364C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="RACI" sheetId="1" r:id="rId1"/>
+    <sheet name="Assumptions" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="42">
   <si>
     <t>Job Tracking</t>
   </si>
@@ -60,9 +61,6 @@
     <t>Create new tracking job</t>
   </si>
   <si>
-    <t>Edit any tracking job</t>
-  </si>
-  <si>
     <t>View any tracking job</t>
   </si>
   <si>
@@ -75,9 +73,6 @@
     <t>Other roles missing?</t>
   </si>
   <si>
-    <t>Edit any processing job</t>
-  </si>
-  <si>
     <t>View any processing job</t>
   </si>
   <si>
@@ -105,22 +100,61 @@
     <t>Submit any SERD file</t>
   </si>
   <si>
-    <t>Upload and preview any CSV file to processing job</t>
-  </si>
-  <si>
-    <t>Upload and preview any SERD file to processing job</t>
-  </si>
-  <si>
-    <t>Remove any SERD file from processing job</t>
-  </si>
-  <si>
-    <t>Remove any CSV file from processing job</t>
-  </si>
-  <si>
     <t>Save any manual observation</t>
   </si>
   <si>
     <t>Save any manual track</t>
+  </si>
+  <si>
+    <t>A processor can see and edit processing jobs of other processors</t>
+  </si>
+  <si>
+    <t>Assumption</t>
+  </si>
+  <si>
+    <t>Upload and preview any CSV file to the processing job</t>
+  </si>
+  <si>
+    <t>Upload and preview any SERD file to the processing job</t>
+  </si>
+  <si>
+    <t>Remove any CSV file from the processing job</t>
+  </si>
+  <si>
+    <t>Remove any SERD file from the processing job</t>
+  </si>
+  <si>
+    <t>Edit any field of any tracking job</t>
+  </si>
+  <si>
+    <t>Option does not exists yet</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>Authorized Layers Only</t>
+  </si>
+  <si>
+    <t>Edit any field of any processing job</t>
+  </si>
+  <si>
+    <t>Only If Assignee</t>
+  </si>
+  <si>
+    <t>Implement: 
+processor should not be able to modify Assigned/Job Type fields
+admin can only assign for processor authorized ot the layer</t>
+  </si>
+  <si>
+    <t>Anyone can change the status field?
+Currently a processor can edit a job, despite not being able to create one</t>
+  </si>
+  <si>
+    <t>Currenlty a processor can change jobs of other assignees</t>
   </si>
 </sst>
 </file>
@@ -180,7 +214,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -188,11 +222,91 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -205,17 +319,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -531,302 +693,550 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8241113-B417-428D-AC32-02353260368C}">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="53.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="51.140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="19"/>
+    </row>
+    <row r="5" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="19"/>
+      <c r="P5" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="23"/>
+      <c r="H6" s="24"/>
+      <c r="P6" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="13"/>
+      <c r="H7" s="14"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="18"/>
+      <c r="H8" s="19"/>
+    </row>
+    <row r="9" spans="1:16" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="18"/>
+      <c r="H9" s="19"/>
+      <c r="P9" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C10" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="18"/>
+      <c r="H10" s="19"/>
+      <c r="P10" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="H11" s="19"/>
+      <c r="P11" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="H12" s="19"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="9"/>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C13" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="19"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C14" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="18"/>
+      <c r="H14" s="19"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
+      <c r="B15" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="18"/>
+      <c r="H15" s="19"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="18"/>
+      <c r="H16" s="19"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="15"/>
+      <c r="B17" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="18"/>
+      <c r="H17" s="19"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="15"/>
+      <c r="B18" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="18"/>
+      <c r="H18" s="19"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C19" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="18"/>
+      <c r="H19" s="19"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="15"/>
+      <c r="B20" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C20" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="18"/>
+      <c r="H20" s="19"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
+      <c r="B21" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="18"/>
+      <c r="H21" s="19"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="C22" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="23"/>
+      <c r="H22" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:A5"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A22"/>
+    <mergeCell ref="C1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4A3D67-1742-49A0-8C5B-B4D8817A675E}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="59.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d161086-4829-409f-9f75-5bde88dcb151">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="42d8e6db-7b1e-4a51-8fbb-e5e83cc76820" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CEAE28352B96D64C95AA0D5E2FA62FAD" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ed183881d36ac1b5d7d67982eda510d1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3d161086-4829-409f-9f75-5bde88dcb151" xmlns:ns3="42d8e6db-7b1e-4a51-8fbb-e5e83cc76820" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="685f4fda20cf913d28bf77c13cd653dd" ns2:_="" ns3:_="">
     <xsd:import namespace="3d161086-4829-409f-9f75-5bde88dcb151"/>
@@ -1049,27 +1459,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D81544A-2E61-425B-A95E-57495CA62CCD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d161086-4829-409f-9f75-5bde88dcb151">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="42d8e6db-7b1e-4a51-8fbb-e5e83cc76820" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50FD7BCE-BCEE-4738-8162-92EEF9AFDC04}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="3d161086-4829-409f-9f75-5bde88dcb151"/>
+    <ds:schemaRef ds:uri="42d8e6db-7b1e-4a51-8fbb-e5e83cc76820"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BADC4E3A-0F8E-4B3C-B98C-96078AA3C813}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1086,29 +1501,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D81544A-2E61-425B-A95E-57495CA62CCD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50FD7BCE-BCEE-4738-8162-92EEF9AFDC04}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="42d8e6db-7b1e-4a51-8fbb-e5e83cc76820"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3d161086-4829-409f-9f75-5bde88dcb151"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>